--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120077357</v>
+        <v>120077351</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486355</v>
+        <v>486687</v>
       </c>
       <c r="R2" t="n">
-        <v>7086966</v>
+        <v>7087458</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120077335</v>
+        <v>120077354</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486442</v>
+        <v>486487</v>
       </c>
       <c r="R3" t="n">
-        <v>7087431</v>
+        <v>7087476</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120077351</v>
+        <v>120077331</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>90527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486687</v>
+        <v>486487</v>
       </c>
       <c r="R4" t="n">
-        <v>7087458</v>
+        <v>7087388</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120077360</v>
+        <v>120077353</v>
       </c>
       <c r="B5" t="n">
-        <v>86878</v>
+        <v>79607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486602</v>
+        <v>486641</v>
       </c>
       <c r="R5" t="n">
-        <v>7087458</v>
+        <v>7087481</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120077345</v>
+        <v>120077335</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>90562</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486683</v>
+        <v>486442</v>
       </c>
       <c r="R6" t="n">
-        <v>7087476</v>
+        <v>7087431</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120077348</v>
+        <v>120077347</v>
       </c>
       <c r="B7" t="n">
         <v>91005</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486449</v>
+        <v>486551</v>
       </c>
       <c r="R7" t="n">
-        <v>7087442</v>
+        <v>7087139</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120077354</v>
+        <v>120077348</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>91005</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486487</v>
+        <v>486449</v>
       </c>
       <c r="R8" t="n">
-        <v>7087476</v>
+        <v>7087442</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120077339</v>
+        <v>120077338</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,39 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486731</v>
+        <v>486434</v>
       </c>
       <c r="R9" t="n">
-        <v>7087577</v>
+        <v>7087220</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120077353</v>
+        <v>120077339</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,34 +1507,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486641</v>
+        <v>486731</v>
       </c>
       <c r="R10" t="n">
-        <v>7087481</v>
+        <v>7087577</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120077349</v>
+        <v>120077336</v>
       </c>
       <c r="B11" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486733</v>
+        <v>486480</v>
       </c>
       <c r="R11" t="n">
-        <v>7087545</v>
+        <v>7087385</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120077336</v>
+        <v>120077358</v>
       </c>
       <c r="B12" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486480</v>
+        <v>486478</v>
       </c>
       <c r="R12" t="n">
-        <v>7087385</v>
+        <v>7087160</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120077355</v>
+        <v>120077340</v>
       </c>
       <c r="B14" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,38 +1916,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486493</v>
+        <v>486641</v>
       </c>
       <c r="R14" t="n">
-        <v>7087479</v>
+        <v>7087454</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2108,10 +2120,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120077356</v>
+        <v>120077345</v>
       </c>
       <c r="B16" t="n">
-        <v>90576</v>
+        <v>79636</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2132,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2160,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486706</v>
+        <v>486683</v>
       </c>
       <c r="R16" t="n">
-        <v>7087531</v>
+        <v>7087476</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120077330</v>
+        <v>120077357</v>
       </c>
       <c r="B17" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2234,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486685</v>
+        <v>486355</v>
       </c>
       <c r="R17" t="n">
-        <v>7087495</v>
+        <v>7086966</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2324,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120077333</v>
+        <v>120077330</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2336,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2364,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486727</v>
+        <v>486685</v>
       </c>
       <c r="R18" t="n">
-        <v>7087535</v>
+        <v>7087495</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2414,10 +2426,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120077347</v>
+        <v>120077355</v>
       </c>
       <c r="B19" t="n">
-        <v>91005</v>
+        <v>79643</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2438,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2466,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486551</v>
+        <v>486493</v>
       </c>
       <c r="R19" t="n">
-        <v>7087139</v>
+        <v>7087479</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2516,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120077350</v>
+        <v>120077329</v>
       </c>
       <c r="B20" t="n">
-        <v>96862</v>
+        <v>95455</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2540,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486584</v>
+        <v>486664</v>
       </c>
       <c r="R20" t="n">
-        <v>7087150</v>
+        <v>7087473</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2618,10 +2630,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120077329</v>
+        <v>120077333</v>
       </c>
       <c r="B21" t="n">
-        <v>95455</v>
+        <v>90562</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2646,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2670,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486664</v>
+        <v>486727</v>
       </c>
       <c r="R21" t="n">
-        <v>7087473</v>
+        <v>7087535</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2720,10 +2732,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120077340</v>
+        <v>120077349</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,46 +2748,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486641</v>
+        <v>486733</v>
       </c>
       <c r="R22" t="n">
-        <v>7087454</v>
+        <v>7087545</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120077352</v>
+        <v>120077356</v>
       </c>
       <c r="B24" t="n">
-        <v>79607</v>
+        <v>90576</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486690</v>
+        <v>486706</v>
       </c>
       <c r="R24" t="n">
-        <v>7087563</v>
+        <v>7087531</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120077331</v>
+        <v>120077352</v>
       </c>
       <c r="B25" t="n">
-        <v>90527</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3050,25 +3050,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486487</v>
+        <v>486690</v>
       </c>
       <c r="R25" t="n">
-        <v>7087388</v>
+        <v>7087563</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3140,10 +3140,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120077358</v>
+        <v>120077360</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>86878</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3156,21 +3156,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486478</v>
+        <v>486602</v>
       </c>
       <c r="R26" t="n">
-        <v>7087160</v>
+        <v>7087458</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120077338</v>
+        <v>120077350</v>
       </c>
       <c r="B27" t="n">
-        <v>90562</v>
+        <v>96862</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3254,25 +3254,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486434</v>
+        <v>486584</v>
       </c>
       <c r="R27" t="n">
-        <v>7087220</v>
+        <v>7087150</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120077351</v>
+        <v>120077331</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>90527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486687</v>
+        <v>486487</v>
       </c>
       <c r="R2" t="n">
-        <v>7087458</v>
+        <v>7087388</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120077354</v>
+        <v>120077351</v>
       </c>
       <c r="B3" t="n">
         <v>79607</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486487</v>
+        <v>486687</v>
       </c>
       <c r="R3" t="n">
-        <v>7087476</v>
+        <v>7087458</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120077331</v>
+        <v>120077354</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
+        <v>79607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>486487</v>
       </c>
       <c r="R4" t="n">
-        <v>7087388</v>
+        <v>7087476</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120077345</v>
+        <v>120077357</v>
       </c>
       <c r="B16" t="n">
-        <v>79636</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2132,25 +2132,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486683</v>
+        <v>486355</v>
       </c>
       <c r="R16" t="n">
-        <v>7087476</v>
+        <v>7086966</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120077357</v>
+        <v>120077330</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>90527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2234,25 +2234,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486355</v>
+        <v>486685</v>
       </c>
       <c r="R17" t="n">
-        <v>7086966</v>
+        <v>7087495</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120077330</v>
+        <v>120077345</v>
       </c>
       <c r="B18" t="n">
-        <v>90527</v>
+        <v>79636</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2340,21 +2340,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486685</v>
+        <v>486683</v>
       </c>
       <c r="R18" t="n">
-        <v>7087495</v>
+        <v>7087476</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120077331</v>
+        <v>120077333</v>
       </c>
       <c r="B2" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486487</v>
+        <v>486727</v>
       </c>
       <c r="R2" t="n">
-        <v>7087388</v>
+        <v>7087535</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120077351</v>
+        <v>120077330</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>90527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486687</v>
+        <v>486685</v>
       </c>
       <c r="R3" t="n">
-        <v>7087458</v>
+        <v>7087495</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120077354</v>
+        <v>120077352</v>
       </c>
       <c r="B4" t="n">
         <v>79607</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486487</v>
+        <v>486690</v>
       </c>
       <c r="R4" t="n">
-        <v>7087476</v>
+        <v>7087563</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120077353</v>
+        <v>120077354</v>
       </c>
       <c r="B5" t="n">
         <v>79607</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486641</v>
+        <v>486487</v>
       </c>
       <c r="R5" t="n">
-        <v>7087481</v>
+        <v>7087476</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120077335</v>
+        <v>120077331</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486442</v>
+        <v>486487</v>
       </c>
       <c r="R6" t="n">
-        <v>7087431</v>
+        <v>7087388</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120077347</v>
+        <v>120077335</v>
       </c>
       <c r="B7" t="n">
-        <v>91005</v>
+        <v>90562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486551</v>
+        <v>486442</v>
       </c>
       <c r="R7" t="n">
-        <v>7087139</v>
+        <v>7087431</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120077348</v>
+        <v>120077334</v>
       </c>
       <c r="B8" t="n">
-        <v>91005</v>
+        <v>90562</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486449</v>
+        <v>486633</v>
       </c>
       <c r="R8" t="n">
-        <v>7087442</v>
+        <v>7087453</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120077338</v>
+        <v>120077358</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486434</v>
+        <v>486478</v>
       </c>
       <c r="R9" t="n">
-        <v>7087220</v>
+        <v>7087160</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120077339</v>
+        <v>120077348</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>91005</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,43 +1503,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486731</v>
+        <v>486449</v>
       </c>
       <c r="R10" t="n">
-        <v>7087577</v>
+        <v>7087442</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120077336</v>
+        <v>120077356</v>
       </c>
       <c r="B11" t="n">
-        <v>90562</v>
+        <v>90576</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486480</v>
+        <v>486706</v>
       </c>
       <c r="R11" t="n">
-        <v>7087385</v>
+        <v>7087531</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120077358</v>
+        <v>120077359</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486478</v>
+        <v>486339</v>
       </c>
       <c r="R12" t="n">
-        <v>7087160</v>
+        <v>7087074</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1904,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120077340</v>
+        <v>120077339</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -1937,29 +1932,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486641</v>
+        <v>486731</v>
       </c>
       <c r="R14" t="n">
-        <v>7087454</v>
+        <v>7087577</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2018,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120077334</v>
+        <v>120077353</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2034,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2058,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486633</v>
+        <v>486641</v>
       </c>
       <c r="R15" t="n">
-        <v>7087453</v>
+        <v>7087481</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2222,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120077330</v>
+        <v>120077338</v>
       </c>
       <c r="B17" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2234,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2262,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486685</v>
+        <v>486434</v>
       </c>
       <c r="R17" t="n">
-        <v>7087495</v>
+        <v>7087220</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2324,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120077345</v>
+        <v>120077336</v>
       </c>
       <c r="B18" t="n">
-        <v>79636</v>
+        <v>90562</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2336,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2364,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486683</v>
+        <v>486480</v>
       </c>
       <c r="R18" t="n">
-        <v>7087476</v>
+        <v>7087385</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2426,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120077355</v>
+        <v>120077329</v>
       </c>
       <c r="B19" t="n">
-        <v>79643</v>
+        <v>95455</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2438,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2466,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486493</v>
+        <v>486664</v>
       </c>
       <c r="R19" t="n">
-        <v>7087479</v>
+        <v>7087473</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2528,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120077329</v>
+        <v>120077355</v>
       </c>
       <c r="B20" t="n">
-        <v>95455</v>
+        <v>79643</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2540,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2568,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486664</v>
+        <v>486493</v>
       </c>
       <c r="R20" t="n">
-        <v>7087473</v>
+        <v>7087479</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2630,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120077333</v>
+        <v>120077349</v>
       </c>
       <c r="B21" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2646,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2670,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486727</v>
+        <v>486733</v>
       </c>
       <c r="R21" t="n">
-        <v>7087535</v>
+        <v>7087545</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2732,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120077349</v>
+        <v>120077360</v>
       </c>
       <c r="B22" t="n">
-        <v>90846</v>
+        <v>86878</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2748,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2772,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486733</v>
+        <v>486602</v>
       </c>
       <c r="R22" t="n">
-        <v>7087545</v>
+        <v>7087458</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2834,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120077359</v>
+        <v>120077351</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2850,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2874,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486339</v>
+        <v>486687</v>
       </c>
       <c r="R23" t="n">
-        <v>7087074</v>
+        <v>7087458</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2936,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120077356</v>
+        <v>120077350</v>
       </c>
       <c r="B24" t="n">
-        <v>90576</v>
+        <v>96862</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2948,25 +2936,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2976,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486706</v>
+        <v>486584</v>
       </c>
       <c r="R24" t="n">
-        <v>7087531</v>
+        <v>7087150</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3038,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120077352</v>
+        <v>120077345</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3050,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3078,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486690</v>
+        <v>486683</v>
       </c>
       <c r="R25" t="n">
-        <v>7087563</v>
+        <v>7087476</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3140,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120077360</v>
+        <v>120077340</v>
       </c>
       <c r="B26" t="n">
-        <v>86878</v>
+        <v>57310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3156,34 +3144,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486602</v>
+        <v>486641</v>
       </c>
       <c r="R26" t="n">
-        <v>7087458</v>
+        <v>7087454</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120077350</v>
+        <v>120077347</v>
       </c>
       <c r="B27" t="n">
-        <v>96862</v>
+        <v>91005</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3254,25 +3254,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486584</v>
+        <v>486551</v>
       </c>
       <c r="R27" t="n">
-        <v>7087150</v>
+        <v>7087139</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120077330</v>
+        <v>120077352</v>
       </c>
       <c r="B3" t="n">
-        <v>90527</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486685</v>
+        <v>486690</v>
       </c>
       <c r="R3" t="n">
-        <v>7087495</v>
+        <v>7087563</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120077352</v>
+        <v>120077354</v>
       </c>
       <c r="B4" t="n">
         <v>79607</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486690</v>
+        <v>486487</v>
       </c>
       <c r="R4" t="n">
-        <v>7087563</v>
+        <v>7087476</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120077354</v>
+        <v>120077330</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>90527</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486487</v>
+        <v>486685</v>
       </c>
       <c r="R5" t="n">
-        <v>7087476</v>
+        <v>7087495</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120077356</v>
+        <v>120077359</v>
       </c>
       <c r="B11" t="n">
-        <v>90576</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486706</v>
+        <v>486339</v>
       </c>
       <c r="R11" t="n">
-        <v>7087531</v>
+        <v>7087074</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120077359</v>
+        <v>120077356</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486339</v>
+        <v>486706</v>
       </c>
       <c r="R12" t="n">
-        <v>7087074</v>
+        <v>7087531</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120077357</v>
+        <v>120077338</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486355</v>
+        <v>486434</v>
       </c>
       <c r="R16" t="n">
-        <v>7086966</v>
+        <v>7087220</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120077338</v>
+        <v>120077357</v>
       </c>
       <c r="B17" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486434</v>
+        <v>486355</v>
       </c>
       <c r="R17" t="n">
-        <v>7087220</v>
+        <v>7086966</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120077333</v>
+        <v>120077330</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486727</v>
+        <v>486685</v>
       </c>
       <c r="R2" t="n">
-        <v>7087535</v>
+        <v>7087495</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120077352</v>
+        <v>120077336</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486690</v>
+        <v>486480</v>
       </c>
       <c r="R3" t="n">
-        <v>7087563</v>
+        <v>7087385</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120077354</v>
+        <v>120077329</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>95455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486487</v>
+        <v>486664</v>
       </c>
       <c r="R4" t="n">
-        <v>7087476</v>
+        <v>7087473</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120077330</v>
+        <v>120077339</v>
       </c>
       <c r="B5" t="n">
-        <v>90527</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486685</v>
+        <v>486731</v>
       </c>
       <c r="R5" t="n">
-        <v>7087495</v>
+        <v>7087577</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120077331</v>
+        <v>120077345</v>
       </c>
       <c r="B6" t="n">
-        <v>90527</v>
+        <v>79636</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486487</v>
+        <v>486683</v>
       </c>
       <c r="R6" t="n">
-        <v>7087388</v>
+        <v>7087476</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120077335</v>
+        <v>120077359</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486442</v>
+        <v>486339</v>
       </c>
       <c r="R7" t="n">
-        <v>7087431</v>
+        <v>7087074</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120077334</v>
+        <v>120077358</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486633</v>
+        <v>486478</v>
       </c>
       <c r="R8" t="n">
-        <v>7087453</v>
+        <v>7087160</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120077358</v>
+        <v>120077340</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1410,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486478</v>
+        <v>486641</v>
       </c>
       <c r="R9" t="n">
-        <v>7087160</v>
+        <v>7087454</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1508,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120077348</v>
+        <v>120077337</v>
       </c>
       <c r="B10" t="n">
-        <v>91005</v>
+        <v>90562</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1520,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486449</v>
+        <v>486434</v>
       </c>
       <c r="R10" t="n">
-        <v>7087442</v>
+        <v>7087243</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1610,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120077359</v>
+        <v>120077348</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>91005</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1622,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1650,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486339</v>
+        <v>486449</v>
       </c>
       <c r="R11" t="n">
-        <v>7087074</v>
+        <v>7087442</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,10 +1712,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120077356</v>
+        <v>120077335</v>
       </c>
       <c r="B12" t="n">
-        <v>90576</v>
+        <v>90562</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1728,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486706</v>
+        <v>486442</v>
       </c>
       <c r="R12" t="n">
-        <v>7087531</v>
+        <v>7087431</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,10 +1814,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120077337</v>
+        <v>120077354</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1830,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486434</v>
+        <v>486487</v>
       </c>
       <c r="R13" t="n">
-        <v>7087243</v>
+        <v>7087476</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1899,10 +1916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120077339</v>
+        <v>120077347</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>91005</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,43 +1928,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486731</v>
+        <v>486551</v>
       </c>
       <c r="R14" t="n">
-        <v>7087577</v>
+        <v>7087139</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2018,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120077353</v>
+        <v>120077355</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>79643</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2030,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2058,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486641</v>
+        <v>486493</v>
       </c>
       <c r="R15" t="n">
-        <v>7087481</v>
+        <v>7087479</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,10 +2120,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120077338</v>
+        <v>120077353</v>
       </c>
       <c r="B16" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2136,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2160,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486434</v>
+        <v>486641</v>
       </c>
       <c r="R16" t="n">
-        <v>7087220</v>
+        <v>7087481</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120077357</v>
+        <v>120077356</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2238,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486355</v>
+        <v>486706</v>
       </c>
       <c r="R17" t="n">
-        <v>7086966</v>
+        <v>7087531</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,7 +2324,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120077336</v>
+        <v>120077333</v>
       </c>
       <c r="B18" t="n">
         <v>90562</v>
@@ -2352,10 +2364,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486480</v>
+        <v>486727</v>
       </c>
       <c r="R18" t="n">
-        <v>7087385</v>
+        <v>7087535</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2414,10 +2426,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120077329</v>
+        <v>120077351</v>
       </c>
       <c r="B19" t="n">
-        <v>95455</v>
+        <v>79607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2442,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2466,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486664</v>
+        <v>486687</v>
       </c>
       <c r="R19" t="n">
-        <v>7087473</v>
+        <v>7087458</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2516,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120077355</v>
+        <v>120077338</v>
       </c>
       <c r="B20" t="n">
-        <v>79643</v>
+        <v>90562</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2540,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486493</v>
+        <v>486434</v>
       </c>
       <c r="R20" t="n">
-        <v>7087479</v>
+        <v>7087220</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2822,10 +2834,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120077351</v>
+        <v>120077331</v>
       </c>
       <c r="B23" t="n">
-        <v>79607</v>
+        <v>90527</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,25 +2846,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2874,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486687</v>
+        <v>486487</v>
       </c>
       <c r="R23" t="n">
-        <v>7087458</v>
+        <v>7087388</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2924,10 +2936,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120077350</v>
+        <v>120077357</v>
       </c>
       <c r="B24" t="n">
-        <v>96862</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,25 +2948,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2976,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486584</v>
+        <v>486355</v>
       </c>
       <c r="R24" t="n">
-        <v>7087150</v>
+        <v>7086966</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3026,10 +3038,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120077345</v>
+        <v>120077350</v>
       </c>
       <c r="B25" t="n">
-        <v>79636</v>
+        <v>96862</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,21 +3054,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3078,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486683</v>
+        <v>486584</v>
       </c>
       <c r="R25" t="n">
-        <v>7087476</v>
+        <v>7087150</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3128,10 +3140,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120077340</v>
+        <v>120077334</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,46 +3156,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486641</v>
+        <v>486633</v>
       </c>
       <c r="R26" t="n">
-        <v>7087454</v>
+        <v>7087453</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120077347</v>
+        <v>120077352</v>
       </c>
       <c r="B27" t="n">
-        <v>91005</v>
+        <v>79607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3254,25 +3254,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486551</v>
+        <v>486690</v>
       </c>
       <c r="R27" t="n">
-        <v>7087139</v>
+        <v>7087563</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120077359</v>
+        <v>120077358</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486339</v>
+        <v>486478</v>
       </c>
       <c r="R7" t="n">
-        <v>7087074</v>
+        <v>7087160</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120077358</v>
+        <v>120077359</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486478</v>
+        <v>486339</v>
       </c>
       <c r="R8" t="n">
-        <v>7087160</v>
+        <v>7087074</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120077358</v>
+        <v>120077359</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486478</v>
+        <v>486339</v>
       </c>
       <c r="R7" t="n">
-        <v>7087160</v>
+        <v>7087074</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120077359</v>
+        <v>120077358</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486339</v>
+        <v>486478</v>
       </c>
       <c r="R8" t="n">
-        <v>7087074</v>
+        <v>7087160</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -1712,10 +1712,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120077335</v>
+        <v>120077354</v>
       </c>
       <c r="B12" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1728,21 +1728,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486442</v>
+        <v>486487</v>
       </c>
       <c r="R12" t="n">
-        <v>7087431</v>
+        <v>7087476</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120077354</v>
+        <v>120077335</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1830,21 +1830,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486487</v>
+        <v>486442</v>
       </c>
       <c r="R13" t="n">
-        <v>7087476</v>
+        <v>7087431</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120077359</v>
+        <v>120077358</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486339</v>
+        <v>486478</v>
       </c>
       <c r="R7" t="n">
-        <v>7087074</v>
+        <v>7087160</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120077358</v>
+        <v>120077359</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486478</v>
+        <v>486339</v>
       </c>
       <c r="R8" t="n">
-        <v>7087160</v>
+        <v>7087074</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120077354</v>
+        <v>120077335</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1728,21 +1728,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486487</v>
+        <v>486442</v>
       </c>
       <c r="R12" t="n">
-        <v>7087476</v>
+        <v>7087431</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120077335</v>
+        <v>120077354</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1830,21 +1830,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486442</v>
+        <v>486487</v>
       </c>
       <c r="R13" t="n">
-        <v>7087431</v>
+        <v>7087476</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120077358</v>
+        <v>120077359</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486478</v>
+        <v>486339</v>
       </c>
       <c r="R7" t="n">
-        <v>7087160</v>
+        <v>7087074</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120077359</v>
+        <v>120077358</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486339</v>
+        <v>486478</v>
       </c>
       <c r="R8" t="n">
-        <v>7087074</v>
+        <v>7087160</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120077335</v>
+        <v>120077354</v>
       </c>
       <c r="B12" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1728,21 +1728,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486442</v>
+        <v>486487</v>
       </c>
       <c r="R12" t="n">
-        <v>7087431</v>
+        <v>7087476</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120077354</v>
+        <v>120077335</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1830,21 +1830,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486487</v>
+        <v>486442</v>
       </c>
       <c r="R13" t="n">
-        <v>7087476</v>
+        <v>7087431</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120077330</v>
+        <v>120077359</v>
       </c>
       <c r="B2" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486685</v>
+        <v>486339</v>
       </c>
       <c r="R2" t="n">
-        <v>7087495</v>
+        <v>7087074</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120077336</v>
+        <v>120077335</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486480</v>
+        <v>486442</v>
       </c>
       <c r="R3" t="n">
-        <v>7087385</v>
+        <v>7087431</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120077329</v>
+        <v>120077349</v>
       </c>
       <c r="B4" t="n">
-        <v>95455</v>
+        <v>90864</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486664</v>
+        <v>486733</v>
       </c>
       <c r="R4" t="n">
-        <v>7087473</v>
+        <v>7087545</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120077339</v>
+        <v>120077334</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,39 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486731</v>
+        <v>486633</v>
       </c>
       <c r="R5" t="n">
-        <v>7087577</v>
+        <v>7087453</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1091,7 +1086,7 @@
         <v>120077345</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>79652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120077359</v>
+        <v>120077351</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486339</v>
+        <v>486687</v>
       </c>
       <c r="R7" t="n">
-        <v>7087074</v>
+        <v>7087458</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120077358</v>
+        <v>120077336</v>
       </c>
       <c r="B8" t="n">
         <v>90580</v>
@@ -1308,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486478</v>
+        <v>486480</v>
       </c>
       <c r="R8" t="n">
-        <v>7087160</v>
+        <v>7087385</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120077340</v>
+        <v>120077337</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,46 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486641</v>
+        <v>486434</v>
       </c>
       <c r="R9" t="n">
-        <v>7087454</v>
+        <v>7087243</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1508,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120077337</v>
+        <v>120077353</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1524,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1548,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486434</v>
+        <v>486641</v>
       </c>
       <c r="R10" t="n">
-        <v>7087243</v>
+        <v>7087481</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1610,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120077348</v>
+        <v>120077338</v>
       </c>
       <c r="B11" t="n">
-        <v>91005</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1622,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1650,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486449</v>
+        <v>486434</v>
       </c>
       <c r="R11" t="n">
-        <v>7087442</v>
+        <v>7087220</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1712,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120077354</v>
+        <v>120077352</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486487</v>
+        <v>486690</v>
       </c>
       <c r="R12" t="n">
-        <v>7087476</v>
+        <v>7087563</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1814,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120077335</v>
+        <v>120077347</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>91023</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1826,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1854,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486442</v>
+        <v>486551</v>
       </c>
       <c r="R13" t="n">
-        <v>7087431</v>
+        <v>7087139</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1916,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120077347</v>
+        <v>120077354</v>
       </c>
       <c r="B14" t="n">
-        <v>91005</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1928,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486551</v>
+        <v>486487</v>
       </c>
       <c r="R14" t="n">
-        <v>7087139</v>
+        <v>7087476</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2018,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120077355</v>
+        <v>120077331</v>
       </c>
       <c r="B15" t="n">
-        <v>79643</v>
+        <v>90545</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2034,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2058,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486493</v>
+        <v>486487</v>
       </c>
       <c r="R15" t="n">
-        <v>7087479</v>
+        <v>7087388</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2120,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120077353</v>
+        <v>120077357</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>90598</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2136,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2160,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486641</v>
+        <v>486355</v>
       </c>
       <c r="R16" t="n">
-        <v>7087481</v>
+        <v>7086966</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2222,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120077356</v>
+        <v>120077330</v>
       </c>
       <c r="B17" t="n">
-        <v>90576</v>
+        <v>90545</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2234,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2262,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486706</v>
+        <v>486685</v>
       </c>
       <c r="R17" t="n">
-        <v>7087531</v>
+        <v>7087495</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2324,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120077333</v>
+        <v>120077340</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2340,34 +2323,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486727</v>
+        <v>486641</v>
       </c>
       <c r="R18" t="n">
-        <v>7087535</v>
+        <v>7087454</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2426,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120077351</v>
+        <v>120077360</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>86895</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2442,21 +2437,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2466,7 +2461,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486687</v>
+        <v>486602</v>
       </c>
       <c r="R19" t="n">
         <v>7087458</v>
@@ -2528,10 +2523,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120077338</v>
+        <v>120077350</v>
       </c>
       <c r="B20" t="n">
-        <v>90562</v>
+        <v>96885</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2540,25 +2535,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2568,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486434</v>
+        <v>486584</v>
       </c>
       <c r="R20" t="n">
-        <v>7087220</v>
+        <v>7087150</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2630,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120077349</v>
+        <v>120077358</v>
       </c>
       <c r="B21" t="n">
-        <v>90846</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2646,21 +2641,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2670,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486733</v>
+        <v>486478</v>
       </c>
       <c r="R21" t="n">
-        <v>7087545</v>
+        <v>7087160</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2732,10 +2727,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120077360</v>
+        <v>120077339</v>
       </c>
       <c r="B22" t="n">
-        <v>86878</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2748,34 +2743,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486602</v>
+        <v>486731</v>
       </c>
       <c r="R22" t="n">
-        <v>7087458</v>
+        <v>7087577</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2834,10 +2834,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120077331</v>
+        <v>120077356</v>
       </c>
       <c r="B23" t="n">
-        <v>90527</v>
+        <v>90594</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2846,25 +2846,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486487</v>
+        <v>486706</v>
       </c>
       <c r="R23" t="n">
-        <v>7087388</v>
+        <v>7087531</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120077357</v>
+        <v>120077329</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486355</v>
+        <v>486664</v>
       </c>
       <c r="R24" t="n">
-        <v>7086966</v>
+        <v>7087473</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120077350</v>
+        <v>120077348</v>
       </c>
       <c r="B25" t="n">
-        <v>96862</v>
+        <v>91023</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3050,25 +3050,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486584</v>
+        <v>486449</v>
       </c>
       <c r="R25" t="n">
-        <v>7087150</v>
+        <v>7087442</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3140,10 +3140,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120077334</v>
+        <v>120077355</v>
       </c>
       <c r="B26" t="n">
-        <v>90562</v>
+        <v>79659</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3152,25 +3152,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486633</v>
+        <v>486493</v>
       </c>
       <c r="R26" t="n">
-        <v>7087453</v>
+        <v>7087479</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120077352</v>
+        <v>120077333</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3258,21 +3258,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486690</v>
+        <v>486727</v>
       </c>
       <c r="R27" t="n">
-        <v>7087563</v>
+        <v>7087535</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120077340</v>
+        <v>120077350</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>96885</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,50 +2319,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486641</v>
+        <v>486584</v>
       </c>
       <c r="R18" t="n">
-        <v>7087454</v>
+        <v>7087150</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2523,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120077350</v>
+        <v>120077358</v>
       </c>
       <c r="B20" t="n">
-        <v>96885</v>
+        <v>90598</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2535,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2563,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486584</v>
+        <v>486478</v>
       </c>
       <c r="R20" t="n">
-        <v>7087150</v>
+        <v>7087160</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2625,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120077358</v>
+        <v>120077339</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,34 +2629,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486478</v>
+        <v>486731</v>
       </c>
       <c r="R21" t="n">
-        <v>7087160</v>
+        <v>7087577</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2727,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120077339</v>
+        <v>120077356</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90594</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2743,39 +2736,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486731</v>
+        <v>486706</v>
       </c>
       <c r="R22" t="n">
-        <v>7087577</v>
+        <v>7087531</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2834,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120077356</v>
+        <v>120077329</v>
       </c>
       <c r="B23" t="n">
-        <v>90594</v>
+        <v>95478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2850,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2874,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486706</v>
+        <v>486664</v>
       </c>
       <c r="R23" t="n">
-        <v>7087531</v>
+        <v>7087473</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2936,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120077329</v>
+        <v>120077348</v>
       </c>
       <c r="B24" t="n">
-        <v>95478</v>
+        <v>91023</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2948,25 +2936,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2976,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486664</v>
+        <v>486449</v>
       </c>
       <c r="R24" t="n">
-        <v>7087473</v>
+        <v>7087442</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3038,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120077348</v>
+        <v>120077355</v>
       </c>
       <c r="B25" t="n">
-        <v>91023</v>
+        <v>79659</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3050,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3078,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486449</v>
+        <v>486493</v>
       </c>
       <c r="R25" t="n">
-        <v>7087442</v>
+        <v>7087479</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3140,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120077355</v>
+        <v>120077333</v>
       </c>
       <c r="B26" t="n">
-        <v>79659</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3152,25 +3140,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3180,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486493</v>
+        <v>486727</v>
       </c>
       <c r="R26" t="n">
-        <v>7087479</v>
+        <v>7087535</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3242,14 +3230,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120077333</v>
+        <v>120077340</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3258,34 +3246,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486727</v>
+        <v>486641</v>
       </c>
       <c r="R27" t="n">
-        <v>7087535</v>
+        <v>7087454</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120077359</v>
+        <v>120077331</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486339</v>
+        <v>486487</v>
       </c>
       <c r="R2" t="n">
-        <v>7087074</v>
+        <v>7087388</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120077335</v>
+        <v>120077329</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486442</v>
+        <v>486664</v>
       </c>
       <c r="R3" t="n">
-        <v>7087431</v>
+        <v>7087473</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120077349</v>
+        <v>120077347</v>
       </c>
       <c r="B4" t="n">
-        <v>90864</v>
+        <v>91023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486733</v>
+        <v>486551</v>
       </c>
       <c r="R4" t="n">
-        <v>7087545</v>
+        <v>7087139</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120077334</v>
+        <v>120077338</v>
       </c>
       <c r="B5" t="n">
         <v>90580</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486633</v>
+        <v>486434</v>
       </c>
       <c r="R5" t="n">
-        <v>7087453</v>
+        <v>7087220</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120077345</v>
+        <v>120077335</v>
       </c>
       <c r="B6" t="n">
-        <v>79652</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486683</v>
+        <v>486442</v>
       </c>
       <c r="R6" t="n">
-        <v>7087476</v>
+        <v>7087431</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120077351</v>
+        <v>120077348</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>91023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486687</v>
+        <v>486449</v>
       </c>
       <c r="R7" t="n">
-        <v>7087458</v>
+        <v>7087442</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120077336</v>
+        <v>120077334</v>
       </c>
       <c r="B8" t="n">
         <v>90580</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486480</v>
+        <v>486633</v>
       </c>
       <c r="R8" t="n">
-        <v>7087385</v>
+        <v>7087453</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120077337</v>
+        <v>120077345</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>79652</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486434</v>
+        <v>486683</v>
       </c>
       <c r="R9" t="n">
-        <v>7087243</v>
+        <v>7087476</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120077353</v>
+        <v>120077339</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,34 +1507,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486641</v>
+        <v>486731</v>
       </c>
       <c r="R10" t="n">
-        <v>7087481</v>
+        <v>7087577</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120077338</v>
+        <v>120077360</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>86895</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486434</v>
+        <v>486602</v>
       </c>
       <c r="R11" t="n">
-        <v>7087220</v>
+        <v>7087458</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120077352</v>
+        <v>120077351</v>
       </c>
       <c r="B12" t="n">
         <v>79623</v>
@@ -1735,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486690</v>
+        <v>486687</v>
       </c>
       <c r="R12" t="n">
-        <v>7087563</v>
+        <v>7087458</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120077347</v>
+        <v>120077356</v>
       </c>
       <c r="B13" t="n">
-        <v>91023</v>
+        <v>90594</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486551</v>
+        <v>486706</v>
       </c>
       <c r="R13" t="n">
-        <v>7087139</v>
+        <v>7087531</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1899,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120077354</v>
+        <v>120077353</v>
       </c>
       <c r="B14" t="n">
         <v>79623</v>
@@ -1939,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486487</v>
+        <v>486641</v>
       </c>
       <c r="R14" t="n">
-        <v>7087476</v>
+        <v>7087481</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120077331</v>
+        <v>120077350</v>
       </c>
       <c r="B15" t="n">
-        <v>90545</v>
+        <v>96885</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486487</v>
+        <v>486584</v>
       </c>
       <c r="R15" t="n">
-        <v>7087388</v>
+        <v>7087150</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2103,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120077357</v>
+        <v>120077349</v>
       </c>
       <c r="B16" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486355</v>
+        <v>486733</v>
       </c>
       <c r="R16" t="n">
-        <v>7086966</v>
+        <v>7087545</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120077330</v>
+        <v>120077352</v>
       </c>
       <c r="B17" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486685</v>
+        <v>486690</v>
       </c>
       <c r="R17" t="n">
-        <v>7087495</v>
+        <v>7087563</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2307,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120077350</v>
+        <v>120077336</v>
       </c>
       <c r="B18" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486584</v>
+        <v>486480</v>
       </c>
       <c r="R18" t="n">
-        <v>7087150</v>
+        <v>7087385</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2409,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120077360</v>
+        <v>120077337</v>
       </c>
       <c r="B19" t="n">
-        <v>86895</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486602</v>
+        <v>486434</v>
       </c>
       <c r="R19" t="n">
-        <v>7087458</v>
+        <v>7087243</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2511,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120077358</v>
+        <v>120077354</v>
       </c>
       <c r="B20" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486478</v>
+        <v>486487</v>
       </c>
       <c r="R20" t="n">
-        <v>7087160</v>
+        <v>7087476</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2613,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120077339</v>
+        <v>120077330</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,43 +2630,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486731</v>
+        <v>486685</v>
       </c>
       <c r="R21" t="n">
-        <v>7087577</v>
+        <v>7087495</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120077356</v>
+        <v>120077355</v>
       </c>
       <c r="B22" t="n">
-        <v>90594</v>
+        <v>79659</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,25 +2732,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486706</v>
+        <v>486493</v>
       </c>
       <c r="R22" t="n">
-        <v>7087531</v>
+        <v>7087479</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120077329</v>
+        <v>120077359</v>
       </c>
       <c r="B23" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486664</v>
+        <v>486339</v>
       </c>
       <c r="R23" t="n">
-        <v>7087473</v>
+        <v>7087074</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120077348</v>
+        <v>120077358</v>
       </c>
       <c r="B24" t="n">
-        <v>91023</v>
+        <v>90598</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,25 +2936,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486449</v>
+        <v>486478</v>
       </c>
       <c r="R24" t="n">
-        <v>7087442</v>
+        <v>7087160</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120077355</v>
+        <v>120077333</v>
       </c>
       <c r="B25" t="n">
-        <v>79659</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486493</v>
+        <v>486727</v>
       </c>
       <c r="R25" t="n">
-        <v>7087479</v>
+        <v>7087535</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120077333</v>
+        <v>120077357</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486727</v>
+        <v>486355</v>
       </c>
       <c r="R26" t="n">
-        <v>7087535</v>
+        <v>7086966</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120077348</v>
+        <v>120077334</v>
       </c>
       <c r="B7" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486449</v>
+        <v>486633</v>
       </c>
       <c r="R7" t="n">
-        <v>7087442</v>
+        <v>7087453</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120077334</v>
+        <v>120077348</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486633</v>
+        <v>486449</v>
       </c>
       <c r="R8" t="n">
-        <v>7087453</v>
+        <v>7087442</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120077356</v>
+        <v>120077353</v>
       </c>
       <c r="B13" t="n">
-        <v>90594</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486706</v>
+        <v>486641</v>
       </c>
       <c r="R13" t="n">
-        <v>7087531</v>
+        <v>7087481</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120077353</v>
+        <v>120077356</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>90594</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486641</v>
+        <v>486706</v>
       </c>
       <c r="R14" t="n">
-        <v>7087481</v>
+        <v>7087531</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120077331</v>
+        <v>120077335</v>
       </c>
       <c r="B2" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486487</v>
+        <v>486442</v>
       </c>
       <c r="R2" t="n">
-        <v>7087388</v>
+        <v>7087431</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120077329</v>
+        <v>120077357</v>
       </c>
       <c r="B3" t="n">
-        <v>95478</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486664</v>
+        <v>486355</v>
       </c>
       <c r="R3" t="n">
-        <v>7087473</v>
+        <v>7086966</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120077347</v>
+        <v>120077345</v>
       </c>
       <c r="B4" t="n">
-        <v>91023</v>
+        <v>79652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486551</v>
+        <v>486683</v>
       </c>
       <c r="R4" t="n">
-        <v>7087139</v>
+        <v>7087476</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120077335</v>
+        <v>120077331</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486442</v>
+        <v>486487</v>
       </c>
       <c r="R6" t="n">
-        <v>7087431</v>
+        <v>7087388</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120077334</v>
+        <v>120077336</v>
       </c>
       <c r="B7" t="n">
         <v>90580</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486633</v>
+        <v>486480</v>
       </c>
       <c r="R7" t="n">
-        <v>7087453</v>
+        <v>7087385</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120077345</v>
+        <v>120077351</v>
       </c>
       <c r="B9" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486683</v>
+        <v>486687</v>
       </c>
       <c r="R9" t="n">
-        <v>7087476</v>
+        <v>7087458</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120077339</v>
+        <v>120077347</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,43 +1503,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486731</v>
+        <v>486551</v>
       </c>
       <c r="R10" t="n">
-        <v>7087577</v>
+        <v>7087139</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120077360</v>
+        <v>120077330</v>
       </c>
       <c r="B11" t="n">
-        <v>86895</v>
+        <v>90545</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486602</v>
+        <v>486685</v>
       </c>
       <c r="R11" t="n">
-        <v>7087458</v>
+        <v>7087495</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120077351</v>
+        <v>120077356</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>90594</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486687</v>
+        <v>486706</v>
       </c>
       <c r="R12" t="n">
-        <v>7087458</v>
+        <v>7087531</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120077353</v>
+        <v>120077329</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>95478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486641</v>
+        <v>486664</v>
       </c>
       <c r="R13" t="n">
-        <v>7087481</v>
+        <v>7087473</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1904,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120077356</v>
+        <v>120077349</v>
       </c>
       <c r="B14" t="n">
-        <v>90594</v>
+        <v>90864</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486706</v>
+        <v>486733</v>
       </c>
       <c r="R14" t="n">
-        <v>7087531</v>
+        <v>7087545</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120077350</v>
+        <v>120077352</v>
       </c>
       <c r="B15" t="n">
-        <v>96885</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486584</v>
+        <v>486690</v>
       </c>
       <c r="R15" t="n">
-        <v>7087150</v>
+        <v>7087563</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120077349</v>
+        <v>120077354</v>
       </c>
       <c r="B16" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486733</v>
+        <v>486487</v>
       </c>
       <c r="R16" t="n">
-        <v>7087545</v>
+        <v>7087476</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120077352</v>
+        <v>120077355</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486690</v>
+        <v>486493</v>
       </c>
       <c r="R17" t="n">
-        <v>7087563</v>
+        <v>7087479</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120077336</v>
+        <v>120077337</v>
       </c>
       <c r="B18" t="n">
         <v>90580</v>
@@ -2352,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486480</v>
+        <v>486434</v>
       </c>
       <c r="R18" t="n">
-        <v>7087385</v>
+        <v>7087243</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2414,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120077337</v>
+        <v>120077334</v>
       </c>
       <c r="B19" t="n">
         <v>90580</v>
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486434</v>
+        <v>486633</v>
       </c>
       <c r="R19" t="n">
-        <v>7087243</v>
+        <v>7087453</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2516,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120077354</v>
+        <v>120077333</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486487</v>
+        <v>486727</v>
       </c>
       <c r="R20" t="n">
-        <v>7087476</v>
+        <v>7087535</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2618,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120077330</v>
+        <v>120077360</v>
       </c>
       <c r="B21" t="n">
-        <v>90545</v>
+        <v>86895</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486685</v>
+        <v>486602</v>
       </c>
       <c r="R21" t="n">
-        <v>7087495</v>
+        <v>7087458</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2720,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120077355</v>
+        <v>120077358</v>
       </c>
       <c r="B22" t="n">
-        <v>79659</v>
+        <v>90598</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,25 +2727,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486493</v>
+        <v>486478</v>
       </c>
       <c r="R22" t="n">
-        <v>7087479</v>
+        <v>7087160</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2924,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120077358</v>
+        <v>120077350</v>
       </c>
       <c r="B24" t="n">
-        <v>90598</v>
+        <v>96885</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,25 +2931,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486478</v>
+        <v>486584</v>
       </c>
       <c r="R24" t="n">
-        <v>7087160</v>
+        <v>7087150</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3026,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120077333</v>
+        <v>120077353</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486727</v>
+        <v>486641</v>
       </c>
       <c r="R25" t="n">
-        <v>7087535</v>
+        <v>7087481</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3128,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120077357</v>
+        <v>120077339</v>
       </c>
       <c r="B26" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,34 +3139,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486355</v>
+        <v>486731</v>
       </c>
       <c r="R26" t="n">
-        <v>7086966</v>
+        <v>7087577</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120077356</v>
+        <v>120077329</v>
       </c>
       <c r="B12" t="n">
-        <v>90594</v>
+        <v>95478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486706</v>
+        <v>486664</v>
       </c>
       <c r="R12" t="n">
-        <v>7087531</v>
+        <v>7087473</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120077329</v>
+        <v>120077356</v>
       </c>
       <c r="B13" t="n">
-        <v>95478</v>
+        <v>90594</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486664</v>
+        <v>486706</v>
       </c>
       <c r="R13" t="n">
-        <v>7087473</v>
+        <v>7087531</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120077335</v>
+        <v>120077349</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486442</v>
+        <v>486733</v>
       </c>
       <c r="R2" t="n">
-        <v>7087431</v>
+        <v>7087545</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120077357</v>
+        <v>120077359</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486355</v>
+        <v>486339</v>
       </c>
       <c r="R3" t="n">
-        <v>7086966</v>
+        <v>7087074</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120077345</v>
+        <v>120077333</v>
       </c>
       <c r="B4" t="n">
-        <v>79652</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486683</v>
+        <v>486727</v>
       </c>
       <c r="R4" t="n">
-        <v>7087476</v>
+        <v>7087535</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120077338</v>
+        <v>120077348</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486434</v>
+        <v>486449</v>
       </c>
       <c r="R5" t="n">
-        <v>7087220</v>
+        <v>7087442</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120077331</v>
+        <v>120077358</v>
       </c>
       <c r="B6" t="n">
-        <v>90545</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486487</v>
+        <v>486478</v>
       </c>
       <c r="R6" t="n">
-        <v>7087388</v>
+        <v>7087160</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120077336</v>
+        <v>120077357</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486480</v>
+        <v>486355</v>
       </c>
       <c r="R7" t="n">
-        <v>7087385</v>
+        <v>7086966</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120077348</v>
+        <v>120077353</v>
       </c>
       <c r="B8" t="n">
-        <v>91023</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486449</v>
+        <v>486641</v>
       </c>
       <c r="R8" t="n">
-        <v>7087442</v>
+        <v>7087481</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120077351</v>
+        <v>120077336</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486687</v>
+        <v>486480</v>
       </c>
       <c r="R9" t="n">
-        <v>7087458</v>
+        <v>7087385</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120077347</v>
+        <v>120077345</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>79652</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486551</v>
+        <v>486683</v>
       </c>
       <c r="R10" t="n">
-        <v>7087139</v>
+        <v>7087476</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120077330</v>
+        <v>120077351</v>
       </c>
       <c r="B11" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486685</v>
+        <v>486687</v>
       </c>
       <c r="R11" t="n">
-        <v>7087495</v>
+        <v>7087458</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120077329</v>
+        <v>120077334</v>
       </c>
       <c r="B12" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486664</v>
+        <v>486633</v>
       </c>
       <c r="R12" t="n">
-        <v>7087473</v>
+        <v>7087453</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120077356</v>
+        <v>120077339</v>
       </c>
       <c r="B13" t="n">
-        <v>90594</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,34 +1813,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486706</v>
+        <v>486731</v>
       </c>
       <c r="R13" t="n">
-        <v>7087531</v>
+        <v>7087577</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1899,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120077349</v>
+        <v>120077335</v>
       </c>
       <c r="B14" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486733</v>
+        <v>486442</v>
       </c>
       <c r="R14" t="n">
-        <v>7087545</v>
+        <v>7087431</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120077352</v>
+        <v>120077347</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>91023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486690</v>
+        <v>486551</v>
       </c>
       <c r="R15" t="n">
-        <v>7087563</v>
+        <v>7087139</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2307,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120077337</v>
+        <v>120077330</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486434</v>
+        <v>486685</v>
       </c>
       <c r="R18" t="n">
-        <v>7087243</v>
+        <v>7087495</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2409,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120077334</v>
+        <v>120077356</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>90594</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486633</v>
+        <v>486706</v>
       </c>
       <c r="R19" t="n">
-        <v>7087453</v>
+        <v>7087531</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2511,7 +2516,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120077333</v>
+        <v>120077337</v>
       </c>
       <c r="B20" t="n">
         <v>90580</v>
@@ -2551,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486727</v>
+        <v>486434</v>
       </c>
       <c r="R20" t="n">
-        <v>7087535</v>
+        <v>7087243</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2613,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120077360</v>
+        <v>120077350</v>
       </c>
       <c r="B21" t="n">
-        <v>86895</v>
+        <v>96885</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486602</v>
+        <v>486584</v>
       </c>
       <c r="R21" t="n">
-        <v>7087458</v>
+        <v>7087150</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2715,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120077358</v>
+        <v>120077352</v>
       </c>
       <c r="B22" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486478</v>
+        <v>486690</v>
       </c>
       <c r="R22" t="n">
-        <v>7087160</v>
+        <v>7087563</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2817,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120077359</v>
+        <v>120077360</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>86895</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486339</v>
+        <v>486602</v>
       </c>
       <c r="R23" t="n">
-        <v>7087074</v>
+        <v>7087458</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2919,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120077350</v>
+        <v>120077329</v>
       </c>
       <c r="B24" t="n">
-        <v>96885</v>
+        <v>95478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2931,25 +2936,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486584</v>
+        <v>486664</v>
       </c>
       <c r="R24" t="n">
-        <v>7087150</v>
+        <v>7087473</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3021,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120077353</v>
+        <v>120077331</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3033,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486641</v>
+        <v>486487</v>
       </c>
       <c r="R25" t="n">
-        <v>7087481</v>
+        <v>7087388</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3123,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120077339</v>
+        <v>120077338</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,39 +3144,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486731</v>
+        <v>486434</v>
       </c>
       <c r="R26" t="n">
-        <v>7087577</v>
+        <v>7087220</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120077349</v>
+        <v>120077337</v>
       </c>
       <c r="B2" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486733</v>
+        <v>486434</v>
       </c>
       <c r="R2" t="n">
-        <v>7087545</v>
+        <v>7087243</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120077359</v>
+        <v>120077331</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486339</v>
+        <v>486487</v>
       </c>
       <c r="R3" t="n">
-        <v>7087074</v>
+        <v>7087388</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120077333</v>
+        <v>120077356</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>90594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486727</v>
+        <v>486706</v>
       </c>
       <c r="R4" t="n">
-        <v>7087535</v>
+        <v>7087531</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120077348</v>
+        <v>120077347</v>
       </c>
       <c r="B5" t="n">
         <v>91023</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486449</v>
+        <v>486551</v>
       </c>
       <c r="R5" t="n">
-        <v>7087442</v>
+        <v>7087139</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120077358</v>
+        <v>120077359</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486478</v>
+        <v>486339</v>
       </c>
       <c r="R6" t="n">
-        <v>7087160</v>
+        <v>7087074</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120077357</v>
+        <v>120077353</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486355</v>
+        <v>486641</v>
       </c>
       <c r="R7" t="n">
-        <v>7086966</v>
+        <v>7087481</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120077353</v>
+        <v>120077349</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486641</v>
+        <v>486733</v>
       </c>
       <c r="R8" t="n">
-        <v>7087481</v>
+        <v>7087545</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120077336</v>
+        <v>120077330</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486480</v>
+        <v>486685</v>
       </c>
       <c r="R9" t="n">
-        <v>7087385</v>
+        <v>7087495</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120077345</v>
+        <v>120077348</v>
       </c>
       <c r="B10" t="n">
-        <v>79652</v>
+        <v>91023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486683</v>
+        <v>486449</v>
       </c>
       <c r="R10" t="n">
-        <v>7087476</v>
+        <v>7087442</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120077351</v>
+        <v>120077338</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486687</v>
+        <v>486434</v>
       </c>
       <c r="R11" t="n">
-        <v>7087458</v>
+        <v>7087220</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120077334</v>
+        <v>120077350</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>96885</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486633</v>
+        <v>486584</v>
       </c>
       <c r="R12" t="n">
-        <v>7087453</v>
+        <v>7087150</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120077335</v>
+        <v>120077333</v>
       </c>
       <c r="B14" t="n">
         <v>90580</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486442</v>
+        <v>486727</v>
       </c>
       <c r="R14" t="n">
-        <v>7087431</v>
+        <v>7087535</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120077347</v>
+        <v>120077354</v>
       </c>
       <c r="B15" t="n">
-        <v>91023</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486551</v>
+        <v>486487</v>
       </c>
       <c r="R15" t="n">
-        <v>7087139</v>
+        <v>7087476</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120077354</v>
+        <v>120077345</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>79652</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486487</v>
+        <v>486683</v>
       </c>
       <c r="R16" t="n">
         <v>7087476</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120077355</v>
+        <v>120077329</v>
       </c>
       <c r="B17" t="n">
-        <v>79659</v>
+        <v>95478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486493</v>
+        <v>486664</v>
       </c>
       <c r="R17" t="n">
-        <v>7087479</v>
+        <v>7087473</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120077330</v>
+        <v>120077360</v>
       </c>
       <c r="B18" t="n">
-        <v>90545</v>
+        <v>86895</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486685</v>
+        <v>486602</v>
       </c>
       <c r="R18" t="n">
-        <v>7087495</v>
+        <v>7087458</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120077356</v>
+        <v>120077357</v>
       </c>
       <c r="B19" t="n">
-        <v>90594</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486706</v>
+        <v>486355</v>
       </c>
       <c r="R19" t="n">
-        <v>7087531</v>
+        <v>7086966</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120077337</v>
+        <v>120077352</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486434</v>
+        <v>486690</v>
       </c>
       <c r="R20" t="n">
-        <v>7087243</v>
+        <v>7087563</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120077350</v>
+        <v>120077334</v>
       </c>
       <c r="B21" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486584</v>
+        <v>486633</v>
       </c>
       <c r="R21" t="n">
-        <v>7087150</v>
+        <v>7087453</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120077352</v>
+        <v>120077351</v>
       </c>
       <c r="B22" t="n">
         <v>79623</v>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486690</v>
+        <v>486687</v>
       </c>
       <c r="R22" t="n">
-        <v>7087563</v>
+        <v>7087458</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120077360</v>
+        <v>120077355</v>
       </c>
       <c r="B23" t="n">
-        <v>86895</v>
+        <v>79659</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,25 +2834,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486602</v>
+        <v>486493</v>
       </c>
       <c r="R23" t="n">
-        <v>7087458</v>
+        <v>7087479</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120077329</v>
+        <v>120077358</v>
       </c>
       <c r="B24" t="n">
-        <v>95478</v>
+        <v>90598</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486664</v>
+        <v>486478</v>
       </c>
       <c r="R24" t="n">
-        <v>7087473</v>
+        <v>7087160</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120077331</v>
+        <v>120077335</v>
       </c>
       <c r="B25" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486487</v>
+        <v>486442</v>
       </c>
       <c r="R25" t="n">
-        <v>7087388</v>
+        <v>7087431</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120077338</v>
+        <v>120077336</v>
       </c>
       <c r="B26" t="n">
         <v>90580</v>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486434</v>
+        <v>486480</v>
       </c>
       <c r="R26" t="n">
-        <v>7087220</v>
+        <v>7087385</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120077333</v>
+        <v>120077354</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486727</v>
+        <v>486487</v>
       </c>
       <c r="R14" t="n">
-        <v>7087535</v>
+        <v>7087476</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120077354</v>
+        <v>120077345</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>79652</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486487</v>
+        <v>486683</v>
       </c>
       <c r="R15" t="n">
         <v>7087476</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120077345</v>
+        <v>120077333</v>
       </c>
       <c r="B16" t="n">
-        <v>79652</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486683</v>
+        <v>486727</v>
       </c>
       <c r="R16" t="n">
-        <v>7087476</v>
+        <v>7087535</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120077329</v>
+        <v>120077357</v>
       </c>
       <c r="B17" t="n">
-        <v>95478</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486664</v>
+        <v>486355</v>
       </c>
       <c r="R17" t="n">
-        <v>7087473</v>
+        <v>7086966</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120077360</v>
+        <v>120077329</v>
       </c>
       <c r="B18" t="n">
-        <v>86895</v>
+        <v>95478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486602</v>
+        <v>486664</v>
       </c>
       <c r="R18" t="n">
-        <v>7087458</v>
+        <v>7087473</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120077357</v>
+        <v>120077360</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>86895</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486355</v>
+        <v>486602</v>
       </c>
       <c r="R19" t="n">
-        <v>7086966</v>
+        <v>7087458</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120077334</v>
+        <v>120077351</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486633</v>
+        <v>486687</v>
       </c>
       <c r="R21" t="n">
-        <v>7087453</v>
+        <v>7087458</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120077351</v>
+        <v>120077334</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486687</v>
+        <v>486633</v>
       </c>
       <c r="R22" t="n">
-        <v>7087458</v>
+        <v>7087453</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120077337</v>
+        <v>120077351</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486434</v>
+        <v>486687</v>
       </c>
       <c r="R2" t="n">
-        <v>7087243</v>
+        <v>7087458</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120077331</v>
+        <v>120077347</v>
       </c>
       <c r="B3" t="n">
-        <v>90545</v>
+        <v>91023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486487</v>
+        <v>486551</v>
       </c>
       <c r="R3" t="n">
-        <v>7087388</v>
+        <v>7087139</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120077356</v>
+        <v>120077352</v>
       </c>
       <c r="B4" t="n">
-        <v>90594</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486706</v>
+        <v>486690</v>
       </c>
       <c r="R4" t="n">
-        <v>7087531</v>
+        <v>7087563</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120077347</v>
+        <v>120077353</v>
       </c>
       <c r="B5" t="n">
-        <v>91023</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486551</v>
+        <v>486641</v>
       </c>
       <c r="R5" t="n">
-        <v>7087139</v>
+        <v>7087481</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120077359</v>
+        <v>120077330</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486339</v>
+        <v>486685</v>
       </c>
       <c r="R6" t="n">
-        <v>7087074</v>
+        <v>7087495</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120077353</v>
+        <v>120077334</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486641</v>
+        <v>486633</v>
       </c>
       <c r="R7" t="n">
-        <v>7087481</v>
+        <v>7087453</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120077349</v>
+        <v>120077355</v>
       </c>
       <c r="B8" t="n">
-        <v>90864</v>
+        <v>79659</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486733</v>
+        <v>486493</v>
       </c>
       <c r="R8" t="n">
-        <v>7087545</v>
+        <v>7087479</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120077330</v>
+        <v>120077357</v>
       </c>
       <c r="B9" t="n">
-        <v>90545</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486685</v>
+        <v>486355</v>
       </c>
       <c r="R9" t="n">
-        <v>7087495</v>
+        <v>7086966</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120077348</v>
+        <v>120077336</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486449</v>
+        <v>486480</v>
       </c>
       <c r="R10" t="n">
-        <v>7087442</v>
+        <v>7087385</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120077338</v>
+        <v>120077354</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486434</v>
+        <v>486487</v>
       </c>
       <c r="R11" t="n">
-        <v>7087220</v>
+        <v>7087476</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120077350</v>
+        <v>120077348</v>
       </c>
       <c r="B12" t="n">
-        <v>96885</v>
+        <v>91023</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486584</v>
+        <v>486449</v>
       </c>
       <c r="R12" t="n">
-        <v>7087150</v>
+        <v>7087442</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120077339</v>
+        <v>120077335</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,39 +1813,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486731</v>
+        <v>486442</v>
       </c>
       <c r="R13" t="n">
-        <v>7087577</v>
+        <v>7087431</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1904,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120077354</v>
+        <v>120077359</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486487</v>
+        <v>486339</v>
       </c>
       <c r="R14" t="n">
-        <v>7087476</v>
+        <v>7087074</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120077345</v>
+        <v>120077331</v>
       </c>
       <c r="B15" t="n">
-        <v>79652</v>
+        <v>90545</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486683</v>
+        <v>486487</v>
       </c>
       <c r="R15" t="n">
-        <v>7087476</v>
+        <v>7087388</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120077333</v>
+        <v>120077349</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486727</v>
+        <v>486733</v>
       </c>
       <c r="R16" t="n">
-        <v>7087535</v>
+        <v>7087545</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120077357</v>
+        <v>120077333</v>
       </c>
       <c r="B17" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486355</v>
+        <v>486727</v>
       </c>
       <c r="R17" t="n">
-        <v>7086966</v>
+        <v>7087535</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120077329</v>
+        <v>120077350</v>
       </c>
       <c r="B18" t="n">
-        <v>95478</v>
+        <v>96885</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486664</v>
+        <v>486584</v>
       </c>
       <c r="R18" t="n">
-        <v>7087473</v>
+        <v>7087150</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2414,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120077360</v>
+        <v>120077338</v>
       </c>
       <c r="B19" t="n">
-        <v>86895</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486602</v>
+        <v>486434</v>
       </c>
       <c r="R19" t="n">
-        <v>7087458</v>
+        <v>7087220</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2516,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120077352</v>
+        <v>120077360</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>86895</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486690</v>
+        <v>486602</v>
       </c>
       <c r="R20" t="n">
-        <v>7087563</v>
+        <v>7087458</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2618,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120077351</v>
+        <v>120077337</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486687</v>
+        <v>486434</v>
       </c>
       <c r="R21" t="n">
-        <v>7087458</v>
+        <v>7087243</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2720,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120077334</v>
+        <v>120077358</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486633</v>
+        <v>486478</v>
       </c>
       <c r="R22" t="n">
-        <v>7087453</v>
+        <v>7087160</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2822,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120077355</v>
+        <v>120077345</v>
       </c>
       <c r="B23" t="n">
-        <v>79659</v>
+        <v>79652</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486493</v>
+        <v>486683</v>
       </c>
       <c r="R23" t="n">
-        <v>7087479</v>
+        <v>7087476</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2924,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120077358</v>
+        <v>120077329</v>
       </c>
       <c r="B24" t="n">
-        <v>90598</v>
+        <v>95478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486478</v>
+        <v>486664</v>
       </c>
       <c r="R24" t="n">
-        <v>7087160</v>
+        <v>7087473</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3026,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120077335</v>
+        <v>120077356</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>90594</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486442</v>
+        <v>486706</v>
       </c>
       <c r="R25" t="n">
-        <v>7087431</v>
+        <v>7087531</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3128,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120077336</v>
+        <v>120077339</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,34 +3139,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486480</v>
+        <v>486731</v>
       </c>
       <c r="R26" t="n">
-        <v>7087385</v>
+        <v>7087577</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120077351</v>
+        <v>120077338</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486687</v>
+        <v>486434</v>
       </c>
       <c r="R2" t="n">
-        <v>7087458</v>
+        <v>7087220</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120077347</v>
+        <v>120077355</v>
       </c>
       <c r="B3" t="n">
-        <v>91023</v>
+        <v>79659</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486551</v>
+        <v>486493</v>
       </c>
       <c r="R3" t="n">
-        <v>7087139</v>
+        <v>7087479</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120077352</v>
+        <v>120077350</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>96885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486690</v>
+        <v>486584</v>
       </c>
       <c r="R4" t="n">
-        <v>7087563</v>
+        <v>7087150</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120077353</v>
+        <v>120077345</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>79652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486641</v>
+        <v>486683</v>
       </c>
       <c r="R5" t="n">
-        <v>7087481</v>
+        <v>7087476</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120077330</v>
+        <v>120077334</v>
       </c>
       <c r="B6" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486685</v>
+        <v>486633</v>
       </c>
       <c r="R6" t="n">
-        <v>7087495</v>
+        <v>7087453</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120077334</v>
+        <v>120077330</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486633</v>
+        <v>486685</v>
       </c>
       <c r="R7" t="n">
-        <v>7087453</v>
+        <v>7087495</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120077355</v>
+        <v>120077335</v>
       </c>
       <c r="B8" t="n">
-        <v>79659</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486493</v>
+        <v>486442</v>
       </c>
       <c r="R8" t="n">
-        <v>7087479</v>
+        <v>7087431</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120077357</v>
+        <v>120077347</v>
       </c>
       <c r="B9" t="n">
-        <v>90598</v>
+        <v>91023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486355</v>
+        <v>486551</v>
       </c>
       <c r="R9" t="n">
-        <v>7086966</v>
+        <v>7087139</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120077336</v>
+        <v>120077353</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486480</v>
+        <v>486641</v>
       </c>
       <c r="R10" t="n">
-        <v>7087385</v>
+        <v>7087481</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120077354</v>
+        <v>120077349</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486487</v>
+        <v>486733</v>
       </c>
       <c r="R11" t="n">
-        <v>7087476</v>
+        <v>7087545</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120077335</v>
+        <v>120077359</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486442</v>
+        <v>486339</v>
       </c>
       <c r="R13" t="n">
-        <v>7087431</v>
+        <v>7087074</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120077359</v>
+        <v>120077358</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486339</v>
+        <v>486478</v>
       </c>
       <c r="R14" t="n">
-        <v>7087074</v>
+        <v>7087160</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120077331</v>
+        <v>120077356</v>
       </c>
       <c r="B15" t="n">
-        <v>90545</v>
+        <v>90594</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486487</v>
+        <v>486706</v>
       </c>
       <c r="R15" t="n">
-        <v>7087388</v>
+        <v>7087531</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120077349</v>
+        <v>120077354</v>
       </c>
       <c r="B16" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486733</v>
+        <v>486487</v>
       </c>
       <c r="R16" t="n">
-        <v>7087545</v>
+        <v>7087476</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120077333</v>
+        <v>120077336</v>
       </c>
       <c r="B17" t="n">
         <v>90580</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486727</v>
+        <v>486480</v>
       </c>
       <c r="R17" t="n">
-        <v>7087535</v>
+        <v>7087385</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120077350</v>
+        <v>120077357</v>
       </c>
       <c r="B18" t="n">
-        <v>96885</v>
+        <v>90598</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486584</v>
+        <v>486355</v>
       </c>
       <c r="R18" t="n">
-        <v>7087150</v>
+        <v>7086966</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120077338</v>
+        <v>120077360</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>86895</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486434</v>
+        <v>486602</v>
       </c>
       <c r="R19" t="n">
-        <v>7087220</v>
+        <v>7087458</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120077360</v>
+        <v>120077339</v>
       </c>
       <c r="B20" t="n">
-        <v>86895</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,34 +2527,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486602</v>
+        <v>486731</v>
       </c>
       <c r="R20" t="n">
-        <v>7087458</v>
+        <v>7087577</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2613,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120077337</v>
+        <v>120077329</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486434</v>
+        <v>486664</v>
       </c>
       <c r="R21" t="n">
-        <v>7087243</v>
+        <v>7087473</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2715,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120077358</v>
+        <v>120077337</v>
       </c>
       <c r="B22" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486478</v>
+        <v>486434</v>
       </c>
       <c r="R22" t="n">
-        <v>7087160</v>
+        <v>7087243</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2817,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120077345</v>
+        <v>120077352</v>
       </c>
       <c r="B23" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2829,25 +2834,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486683</v>
+        <v>486690</v>
       </c>
       <c r="R23" t="n">
-        <v>7087476</v>
+        <v>7087563</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2919,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120077329</v>
+        <v>120077331</v>
       </c>
       <c r="B24" t="n">
-        <v>95478</v>
+        <v>90545</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2931,25 +2936,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486664</v>
+        <v>486487</v>
       </c>
       <c r="R24" t="n">
-        <v>7087473</v>
+        <v>7087388</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3021,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120077356</v>
+        <v>120077351</v>
       </c>
       <c r="B25" t="n">
-        <v>90594</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486706</v>
+        <v>486687</v>
       </c>
       <c r="R25" t="n">
-        <v>7087531</v>
+        <v>7087458</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3123,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120077339</v>
+        <v>120077333</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,39 +3144,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486731</v>
+        <v>486727</v>
       </c>
       <c r="R26" t="n">
-        <v>7087577</v>
+        <v>7087535</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120077338</v>
+        <v>120077350</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>96885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486434</v>
+        <v>486584</v>
       </c>
       <c r="R2" t="n">
-        <v>7087220</v>
+        <v>7087150</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120077355</v>
+        <v>120077338</v>
       </c>
       <c r="B3" t="n">
-        <v>79659</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486493</v>
+        <v>486434</v>
       </c>
       <c r="R3" t="n">
-        <v>7087479</v>
+        <v>7087220</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120077350</v>
+        <v>120077355</v>
       </c>
       <c r="B4" t="n">
-        <v>96885</v>
+        <v>79659</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486584</v>
+        <v>486493</v>
       </c>
       <c r="R4" t="n">
-        <v>7087150</v>
+        <v>7087479</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120077349</v>
+        <v>120077329</v>
       </c>
       <c r="B2" t="n">
-        <v>90864</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486733</v>
+        <v>486664</v>
       </c>
       <c r="R2" t="n">
-        <v>7087545</v>
+        <v>7087473</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120077333</v>
+        <v>120077360</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486727</v>
+        <v>486602</v>
       </c>
       <c r="R3" t="n">
-        <v>7087535</v>
+        <v>7087458</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120077330</v>
+        <v>120077349</v>
       </c>
       <c r="B4" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486685</v>
+        <v>486733</v>
       </c>
       <c r="R4" t="n">
-        <v>7087495</v>
+        <v>7087545</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120077329</v>
+        <v>120077333</v>
       </c>
       <c r="B5" t="n">
-        <v>95478</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486664</v>
+        <v>486727</v>
       </c>
       <c r="R5" t="n">
-        <v>7087473</v>
+        <v>7087535</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120077338</v>
+        <v>120077334</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486434</v>
+        <v>486633</v>
       </c>
       <c r="R6" t="n">
-        <v>7087220</v>
+        <v>7087453</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120077348</v>
+        <v>120077335</v>
       </c>
       <c r="B7" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486449</v>
+        <v>486442</v>
       </c>
       <c r="R7" t="n">
-        <v>7087442</v>
+        <v>7087431</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120077339</v>
+        <v>120077336</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,39 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486731</v>
+        <v>486480</v>
       </c>
       <c r="R8" t="n">
-        <v>7087577</v>
+        <v>7087385</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120077354</v>
+        <v>120077337</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486487</v>
+        <v>486434</v>
       </c>
       <c r="R9" t="n">
-        <v>7087476</v>
+        <v>7087243</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120077335</v>
+        <v>120077338</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1536,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486442</v>
+        <v>486434</v>
       </c>
       <c r="R10" t="n">
-        <v>7087431</v>
+        <v>7087220</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120077334</v>
+        <v>120077356</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486633</v>
+        <v>486706</v>
       </c>
       <c r="R11" t="n">
-        <v>7087453</v>
+        <v>7087531</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120077359</v>
+        <v>120077347</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486339</v>
+        <v>486551</v>
       </c>
       <c r="R12" t="n">
-        <v>7087074</v>
+        <v>7087139</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120077353</v>
+        <v>120077348</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486641</v>
+        <v>486449</v>
       </c>
       <c r="R13" t="n">
-        <v>7087481</v>
+        <v>7087442</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1904,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120077345</v>
+        <v>120077330</v>
       </c>
       <c r="B14" t="n">
-        <v>79652</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486683</v>
+        <v>486685</v>
       </c>
       <c r="R14" t="n">
-        <v>7087476</v>
+        <v>7087495</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120077360</v>
+        <v>120077331</v>
       </c>
       <c r="B15" t="n">
-        <v>86895</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486602</v>
+        <v>486487</v>
       </c>
       <c r="R15" t="n">
-        <v>7087458</v>
+        <v>7087388</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120077350</v>
+        <v>120077359</v>
       </c>
       <c r="B16" t="n">
-        <v>96885</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486584</v>
+        <v>486339</v>
       </c>
       <c r="R16" t="n">
-        <v>7087150</v>
+        <v>7087074</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120077337</v>
+        <v>120077351</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486434</v>
+        <v>486687</v>
       </c>
       <c r="R17" t="n">
-        <v>7087243</v>
+        <v>7087458</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120077331</v>
+        <v>120077352</v>
       </c>
       <c r="B18" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486487</v>
+        <v>486690</v>
       </c>
       <c r="R18" t="n">
-        <v>7087388</v>
+        <v>7087563</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2414,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120077356</v>
+        <v>120077353</v>
       </c>
       <c r="B19" t="n">
-        <v>90594</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486706</v>
+        <v>486641</v>
       </c>
       <c r="R19" t="n">
-        <v>7087531</v>
+        <v>7087481</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2516,37 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120077347</v>
+        <v>120077354</v>
       </c>
       <c r="B20" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486551</v>
+        <v>486487</v>
       </c>
       <c r="R20" t="n">
-        <v>7087139</v>
+        <v>7087476</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2618,37 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120077358</v>
+        <v>120077345</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486478</v>
+        <v>486683</v>
       </c>
       <c r="R21" t="n">
-        <v>7087160</v>
+        <v>7087476</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2720,37 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120077357</v>
+        <v>120077355</v>
       </c>
       <c r="B22" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486355</v>
+        <v>486493</v>
       </c>
       <c r="R22" t="n">
-        <v>7086966</v>
+        <v>7087479</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2822,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120077336</v>
+        <v>120077339</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2838,34 +2723,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486480</v>
+        <v>486731</v>
       </c>
       <c r="R23" t="n">
-        <v>7087385</v>
+        <v>7087577</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2924,15 +2814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120077351</v>
+        <v>120077340</v>
       </c>
       <c r="B24" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2940,34 +2825,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486687</v>
+        <v>486641</v>
       </c>
       <c r="R24" t="n">
-        <v>7087458</v>
+        <v>7087454</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3006,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -3026,15 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120077352</v>
+        <v>120077341</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,34 +2934,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mörttjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486690</v>
+        <v>486416</v>
       </c>
       <c r="R25" t="n">
-        <v>7087563</v>
+        <v>7087467</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3128,15 +3025,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120077355</v>
+        <v>120077350</v>
       </c>
       <c r="B26" t="n">
-        <v>79659</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3036,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3060,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486493</v>
+        <v>486584</v>
       </c>
       <c r="R26" t="n">
-        <v>7087479</v>
+        <v>7087150</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3227,120 +3119,6 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>120077340</v>
-      </c>
-      <c r="B27" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Mörttjärnflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>486641</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7087454</v>
-      </c>
-      <c r="S27" t="n">
-        <v>15</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Laxsjö</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19403-2024 artfynd.xlsx
+++ b/artfynd/A 19403-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077329</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077360</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077349</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077333</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077334</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077335</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077336</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077337</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077338</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077356</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077347</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077348</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077330</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077331</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077359</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077351</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077352</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077353</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077354</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077345</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077355</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2811,6 +2921,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077339</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2920,6 +3035,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077340</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3022,6 +3142,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077341</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3119,8 +3244,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120077350</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>